--- a/data/trans_bre/P1802_2016_2023-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1802_2016_2023-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,49</t>
+          <t>3,05; 10,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,34</t>
+          <t>-1,72; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 71,3</t>
+          <t>16,42; 71,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 25,17</t>
+          <t>-8,44; 34,7</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-9,21</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-38,04%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,15</t>
+          <t>1,45; 6,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 1,01</t>
+          <t>0,9; 5,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 50,2</t>
+          <t>10,07; 47,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 6,97</t>
+          <t>5,72; 40,08</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 7,24</t>
+          <t>-1,81; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,64</t>
+          <t>1,57; 9,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 66,32</t>
+          <t>-11,16; 62,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 75,6</t>
+          <t>8,78; 72,87</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-21,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,32</t>
+          <t>2,68; 6,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 1,97</t>
+          <t>1,94; 5,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 46,77</t>
+          <t>18,28; 48,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 12,0</t>
+          <t>12,09; 38,37</t>
         </is>
       </c>
     </row>
